--- a/docs/卡单明细_2026-07-11.xlsx
+++ b/docs/卡单明细_2026-07-11.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,52 +417,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>客户ID</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>客户省份</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>订单编号</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>实付GMV</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>异常原因分类</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>业绩归属</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>下单BD工号</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>下单BD</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>下单BD组别</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>大区</t>
         </is>
@@ -2809,11 +2797,7 @@
           <t>POP</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>公海</t>
-        </is>
-      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
@@ -5055,11 +5039,7 @@
           <t>自营</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>公海</t>
-        </is>
-      </c>
+      <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
@@ -6197,11 +6177,7 @@
           <t>自营</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>公海</t>
-        </is>
-      </c>
+      <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
@@ -15499,11 +15475,7 @@
           <t>自营</t>
         </is>
       </c>
-      <c r="G303" t="inlineStr">
-        <is>
-          <t>公海</t>
-        </is>
-      </c>
+      <c r="G303" t="inlineStr"/>
       <c r="H303" t="inlineStr"/>
       <c r="I303" t="inlineStr">
         <is>
@@ -16445,11 +16417,7 @@
           <t>POP</t>
         </is>
       </c>
-      <c r="G322" t="inlineStr">
-        <is>
-          <t>公海</t>
-        </is>
-      </c>
+      <c r="G322" t="inlineStr"/>
       <c r="H322" t="inlineStr"/>
       <c r="I322" t="inlineStr">
         <is>
@@ -18237,11 +18205,7 @@
           <t>POP</t>
         </is>
       </c>
-      <c r="G358" t="inlineStr">
-        <is>
-          <t>公海</t>
-        </is>
-      </c>
+      <c r="G358" t="inlineStr"/>
       <c r="H358" t="inlineStr"/>
       <c r="I358" t="inlineStr">
         <is>
@@ -20079,11 +20043,7 @@
           <t>自营</t>
         </is>
       </c>
-      <c r="G395" t="inlineStr">
-        <is>
-          <t>公海</t>
-        </is>
-      </c>
+      <c r="G395" t="inlineStr"/>
       <c r="H395" t="inlineStr"/>
       <c r="I395" t="inlineStr">
         <is>
@@ -21725,11 +21685,7 @@
           <t>自营</t>
         </is>
       </c>
-      <c r="G428" t="inlineStr">
-        <is>
-          <t>公海</t>
-        </is>
-      </c>
+      <c r="G428" t="inlineStr"/>
       <c r="H428" t="inlineStr"/>
       <c r="I428" t="inlineStr">
         <is>
@@ -24471,11 +24427,7 @@
           <t>POP</t>
         </is>
       </c>
-      <c r="G483" t="inlineStr">
-        <is>
-          <t>公海</t>
-        </is>
-      </c>
+      <c r="G483" t="inlineStr"/>
       <c r="H483" t="inlineStr"/>
       <c r="I483" t="inlineStr">
         <is>
@@ -28505,11 +28457,7 @@
           <t>POP</t>
         </is>
       </c>
-      <c r="G564" t="inlineStr">
-        <is>
-          <t>公海</t>
-        </is>
-      </c>
+      <c r="G564" t="inlineStr"/>
       <c r="H564" t="inlineStr"/>
       <c r="I564" t="inlineStr">
         <is>
@@ -33643,11 +33591,7 @@
           <t>POP</t>
         </is>
       </c>
-      <c r="G667" t="inlineStr">
-        <is>
-          <t>公海</t>
-        </is>
-      </c>
+      <c r="G667" t="inlineStr"/>
       <c r="H667" t="inlineStr"/>
       <c r="I667" t="inlineStr">
         <is>
@@ -37389,11 +37333,7 @@
           <t>POP</t>
         </is>
       </c>
-      <c r="G742" t="inlineStr">
-        <is>
-          <t>公海</t>
-        </is>
-      </c>
+      <c r="G742" t="inlineStr"/>
       <c r="H742" t="inlineStr"/>
       <c r="I742" t="inlineStr">
         <is>
@@ -38035,11 +37975,7 @@
           <t>POP</t>
         </is>
       </c>
-      <c r="G755" t="inlineStr">
-        <is>
-          <t>公海</t>
-        </is>
-      </c>
+      <c r="G755" t="inlineStr"/>
       <c r="H755" t="inlineStr"/>
       <c r="I755" t="inlineStr">
         <is>
@@ -42319,11 +42255,7 @@
           <t>POP</t>
         </is>
       </c>
-      <c r="G841" t="inlineStr">
-        <is>
-          <t>公海</t>
-        </is>
-      </c>
+      <c r="G841" t="inlineStr"/>
       <c r="H841" t="inlineStr"/>
       <c r="I841" t="inlineStr">
         <is>
@@ -42715,11 +42647,7 @@
           <t>控销</t>
         </is>
       </c>
-      <c r="G849" t="inlineStr">
-        <is>
-          <t>公海</t>
-        </is>
-      </c>
+      <c r="G849" t="inlineStr"/>
       <c r="H849" t="inlineStr"/>
       <c r="I849" t="inlineStr">
         <is>

--- a/docs/卡单明细_2026-07-11.xlsx
+++ b/docs/卡单明细_2026-07-11.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,52 +429,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>客户ID</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>客户省份</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>订单编号</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>实付GMV</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>异常原因分类</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>业绩归属</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>下单BD工号</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>下单BD</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>下单BD组别</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>大区</t>
         </is>
@@ -2797,7 +2809,11 @@
           <t>POP</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
@@ -5039,7 +5055,11 @@
           <t>自营</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
@@ -6177,7 +6197,11 @@
           <t>自营</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
@@ -15475,7 +15499,11 @@
           <t>自营</t>
         </is>
       </c>
-      <c r="G303" t="inlineStr"/>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
       <c r="H303" t="inlineStr"/>
       <c r="I303" t="inlineStr">
         <is>
@@ -16417,7 +16445,11 @@
           <t>POP</t>
         </is>
       </c>
-      <c r="G322" t="inlineStr"/>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
       <c r="H322" t="inlineStr"/>
       <c r="I322" t="inlineStr">
         <is>
@@ -18205,7 +18237,11 @@
           <t>POP</t>
         </is>
       </c>
-      <c r="G358" t="inlineStr"/>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
       <c r="H358" t="inlineStr"/>
       <c r="I358" t="inlineStr">
         <is>
@@ -20043,7 +20079,11 @@
           <t>自营</t>
         </is>
       </c>
-      <c r="G395" t="inlineStr"/>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
       <c r="H395" t="inlineStr"/>
       <c r="I395" t="inlineStr">
         <is>
@@ -21685,7 +21725,11 @@
           <t>自营</t>
         </is>
       </c>
-      <c r="G428" t="inlineStr"/>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
       <c r="H428" t="inlineStr"/>
       <c r="I428" t="inlineStr">
         <is>
@@ -24427,7 +24471,11 @@
           <t>POP</t>
         </is>
       </c>
-      <c r="G483" t="inlineStr"/>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
       <c r="H483" t="inlineStr"/>
       <c r="I483" t="inlineStr">
         <is>
@@ -28457,7 +28505,11 @@
           <t>POP</t>
         </is>
       </c>
-      <c r="G564" t="inlineStr"/>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
       <c r="H564" t="inlineStr"/>
       <c r="I564" t="inlineStr">
         <is>
@@ -33591,7 +33643,11 @@
           <t>POP</t>
         </is>
       </c>
-      <c r="G667" t="inlineStr"/>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
       <c r="H667" t="inlineStr"/>
       <c r="I667" t="inlineStr">
         <is>
@@ -37333,7 +37389,11 @@
           <t>POP</t>
         </is>
       </c>
-      <c r="G742" t="inlineStr"/>
+      <c r="G742" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
       <c r="H742" t="inlineStr"/>
       <c r="I742" t="inlineStr">
         <is>
@@ -37975,7 +38035,11 @@
           <t>POP</t>
         </is>
       </c>
-      <c r="G755" t="inlineStr"/>
+      <c r="G755" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
       <c r="H755" t="inlineStr"/>
       <c r="I755" t="inlineStr">
         <is>
@@ -42255,7 +42319,11 @@
           <t>POP</t>
         </is>
       </c>
-      <c r="G841" t="inlineStr"/>
+      <c r="G841" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
       <c r="H841" t="inlineStr"/>
       <c r="I841" t="inlineStr">
         <is>
@@ -42647,7 +42715,11 @@
           <t>控销</t>
         </is>
       </c>
-      <c r="G849" t="inlineStr"/>
+      <c r="G849" t="inlineStr">
+        <is>
+          <t>公海</t>
+        </is>
+      </c>
       <c r="H849" t="inlineStr"/>
       <c r="I849" t="inlineStr">
         <is>
